--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdDepositInvestTrade001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdDepositInvestTrade001.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15525" windowHeight="4125"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>组合代码</t>
   </si>
@@ -64,6 +64,10 @@
   </si>
   <si>
     <t>资产四级分类</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合作资产</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -115,74 +119,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -195,11 +131,11 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="373737"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
         <a:sysClr val="window" lastClr="FFFFFF"/>
@@ -237,7 +173,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -272,7 +208,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -481,10 +417,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -501,33 +437,36 @@
         <v>1</v>
       </c>
       <c r="F1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>12</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>13</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>14</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>6</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>7</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>8</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>9</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>10</v>
       </c>
     </row>

--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdDepositInvestTrade001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdDepositInvestTrade001.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>组合代码</t>
   </si>
@@ -64,10 +64,6 @@
   </si>
   <si>
     <t>资产四级分类</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>合作资产</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -417,10 +413,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -437,36 +433,33 @@
         <v>1</v>
       </c>
       <c r="F1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K1" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O1" t="s">
-        <v>9</v>
-      </c>
-      <c r="P1" t="s">
         <v>10</v>
       </c>
     </row>
